--- a/data/trans_orig/P1419-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2007</t>
+          <t>Población con diagnóstico de varices en las piernas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453543</t>
+          <t>453545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464678</t>
+          <t>465139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>947039</t>
+          <t>947032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>958756</t>
+          <t>959157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>27925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53285</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>717891</t>
+          <t>718378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731741</t>
+          <t>731970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>580395</t>
+          <t>580675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604687</t>
+          <t>604381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1307697</t>
+          <t>1306618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1333581</t>
+          <t>1333057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>64260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46653</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76423</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620986</t>
+          <t>621162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634059</t>
+          <t>633340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624549</t>
+          <t>625484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651924</t>
+          <t>651773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251989</t>
+          <t>1252165</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1281759</t>
+          <t>1282145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32717</t>
+          <t>31576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41839</t>
+          <t>41969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59391</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94756</t>
+          <t>93991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486430</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506635</t>
+          <t>506294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446430</t>
+          <t>447101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473803</t>
+          <t>473673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>940033</t>
+          <t>940798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>975398</t>
+          <t>976258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>49019</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75859</t>
+          <t>77177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67894</t>
+          <t>69316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102938</t>
+          <t>102552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>355535</t>
+          <t>354354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372822</t>
+          <t>372961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328127</t>
+          <t>326809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>355725</t>
+          <t>354967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687758</t>
+          <t>688144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>722802</t>
+          <t>721380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62729</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91576</t>
+          <t>92277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79121</t>
+          <t>80536</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112907</t>
+          <t>113798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263713</t>
+          <t>263836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280886</t>
+          <t>280622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251358</t>
+          <t>250657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280205</t>
+          <t>279945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522610</t>
+          <t>521719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>556396</t>
+          <t>554981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69809</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101650</t>
+          <t>100881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84681</t>
+          <t>84881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124001</t>
+          <t>122889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180837</t>
+          <t>182378</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197785</t>
+          <t>198561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232258</t>
+          <t>233027</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>264099</t>
+          <t>266514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419790</t>
+          <t>420902</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>459110</t>
+          <t>458910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>80228</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118709</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>331117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>402469</t>
+          <t>402712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>422231</t>
+          <t>424119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>507266</t>
+          <t>505612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3157834</t>
+          <t>3157309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3194502</t>
+          <t>3196315</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2976728</t>
+          <t>2976485</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3049580</t>
+          <t>3048080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6148475</t>
+          <t>6150129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6233510</t>
+          <t>6231622</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2012</t>
+          <t>Población con diagnóstico de varices en las piernas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>679662</t>
+          <t>678941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>686142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>596562</t>
+          <t>595892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607415</t>
+          <t>607326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279935</t>
+          <t>1280223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1292456</t>
+          <t>1292412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28346</t>
+          <t>28528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55019</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666975</t>
+          <t>665910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680049</t>
+          <t>679973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654555</t>
+          <t>655441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681228</t>
+          <t>681046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1329455</t>
+          <t>1328596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1358628</t>
+          <t>1358489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53796</t>
+          <t>54890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37442</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>66715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>595317</t>
+          <t>594880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610348</t>
+          <t>610153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>560468</t>
+          <t>559374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>585241</t>
+          <t>585810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161942</t>
+          <t>1162165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191438</t>
+          <t>1192035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12707</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73373</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50349</t>
+          <t>48226</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81864</t>
+          <t>81776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>416722</t>
+          <t>417652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427367</t>
+          <t>427382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>374427</t>
+          <t>371987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402520</t>
+          <t>401361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>795365</t>
+          <t>795453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>826880</t>
+          <t>829003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>43208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69385</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>50961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81075</t>
+          <t>81998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292617</t>
+          <t>292970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304890</t>
+          <t>305768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284611</t>
+          <t>283944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311278</t>
+          <t>310788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>582707</t>
+          <t>581784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>614132</t>
+          <t>612821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79977</t>
+          <t>80521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115371</t>
+          <t>116079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86538</t>
+          <t>86168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125818</t>
+          <t>127247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234786</t>
+          <t>234490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246595</t>
+          <t>246338</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273608</t>
+          <t>272900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309002</t>
+          <t>308458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>513012</t>
+          <t>511583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>552292</t>
+          <t>552662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264972</t>
+          <t>268434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330767</t>
+          <t>337083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>300661</t>
+          <t>301477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>377543</t>
+          <t>376641</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3370587</t>
+          <t>3370687</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3396994</t>
+          <t>3398568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3224331</t>
+          <t>3218015</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3290126</t>
+          <t>3286664</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6604334</t>
+          <t>6605236</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6681216</t>
+          <t>6680400</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2016</t>
+          <t>Población con diagnóstico de varices en las piernas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584114</t>
+          <t>585218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553984</t>
+          <t>554110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562601</t>
+          <t>562604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1142362</t>
+          <t>1143067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152205</t>
+          <t>1152196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660626</t>
+          <t>661494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640095</t>
+          <t>640344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654615</t>
+          <t>654578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1308067</t>
+          <t>1307891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1322312</t>
+          <t>1322469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>50630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72050</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618186</t>
+          <t>615887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635325</t>
+          <t>635371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599172</t>
+          <t>598447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623372</t>
+          <t>623032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1223075</t>
+          <t>1222806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1253390</t>
+          <t>1252383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34927</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63469</t>
+          <t>62635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>44576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>74186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459531</t>
+          <t>458724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473084</t>
+          <t>472929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>433380</t>
+          <t>434214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>461922</t>
+          <t>461954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>898931</t>
+          <t>900581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932235</t>
+          <t>930191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>41534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70713</t>
+          <t>70281</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81881</t>
+          <t>81209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>316251</t>
+          <t>315193</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329298</t>
+          <t>328717</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>307481</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337386</t>
+          <t>336228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630211</t>
+          <t>630883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661353</t>
+          <t>662269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81778</t>
+          <t>80647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>56924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93933</t>
+          <t>94370</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238027</t>
+          <t>237666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251616</t>
+          <t>251075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318391</t>
+          <t>319522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351459</t>
+          <t>351993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>563234</t>
+          <t>562797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>599383</t>
+          <t>600243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39669</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>66907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190504</t>
+          <t>187489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>250283</t>
+          <t>251019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238736</t>
+          <t>238950</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>304018</t>
+          <t>307574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3325367</t>
+          <t>3327443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3354681</t>
+          <t>3354627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3294259</t>
+          <t>3293523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3354038</t>
+          <t>3357053</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6634874</t>
+          <t>6631318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6700156</t>
+          <t>6699942</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2023</t>
+          <t>Población con diagnóstico de varices en las piernas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15385</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>4323</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14467</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>18519</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>13615</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298733</t>
+          <t>297815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>699572</t>
+          <t>694668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415080</t>
+          <t>415473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497472</t>
+          <t>498289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509101</t>
+          <t>509265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>918192</t>
+          <t>918344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931023</t>
+          <t>931093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24472</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43690</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57031</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515958</t>
+          <t>515988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530410</t>
+          <t>531064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>498109</t>
+          <t>498330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>517327</t>
+          <t>517522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1021106</t>
+          <t>1020835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1044028</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70749</t>
+          <t>71489</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101969</t>
+          <t>101838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64984</t>
+          <t>61832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138013</t>
+          <t>137805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849424</t>
+          <t>850198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878346</t>
+          <t>879046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609806</t>
+          <t>609937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641026</t>
+          <t>640286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1461548</t>
+          <t>1461756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1534577</t>
+          <t>1537729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28183</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50260</t>
+          <t>50765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85661</t>
+          <t>84830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95951</t>
+          <t>96291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129499</t>
+          <t>129257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509977</t>
+          <t>509472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532054</t>
+          <t>530899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>459067</t>
+          <t>459898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>483617</t>
+          <t>482966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975465</t>
+          <t>975707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1009013</t>
+          <t>1008673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26467</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>99415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39634</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112515</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>337992</t>
+          <t>336968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>352210</t>
+          <t>352333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>508241</t>
+          <t>508953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>581901</t>
+          <t>580345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>863299</t>
+          <t>864264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>936180</t>
+          <t>935648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88526</t>
+          <t>88542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>113299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111197</t>
+          <t>109600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139191</t>
+          <t>141643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249552</t>
+          <t>249858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264640</t>
+          <t>265525</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>311465</t>
+          <t>312532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>337305</t>
+          <t>337289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>569399</t>
+          <t>566947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597393</t>
+          <t>598990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94642</t>
+          <t>93768</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145440</t>
+          <t>145705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>303230</t>
+          <t>301167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>405612</t>
+          <t>407814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>427074</t>
+          <t>428811</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>534207</t>
+          <t>538558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3312661</t>
+          <t>3312396</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3363459</t>
+          <t>3364333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3251592</t>
+          <t>3249390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3353974</t>
+          <t>3356037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6581099</t>
+          <t>6576748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6688232</t>
+          <t>6686495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1419-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Edad-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453545</t>
+          <t>454133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>465139</t>
+          <t>465157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>947032</t>
+          <t>947994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959157</t>
+          <t>958859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44819</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>27902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>54804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>718378</t>
+          <t>718260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731970</t>
+          <t>731813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>580675</t>
+          <t>582306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604381</t>
+          <t>604472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1306618</t>
+          <t>1306178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1333057</t>
+          <t>1333080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37971</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64260</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>46057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621162</t>
+          <t>619852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633340</t>
+          <t>633857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625484</t>
+          <t>623311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651773</t>
+          <t>652135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252165</t>
+          <t>1250499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282145</t>
+          <t>1282355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31576</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41969</t>
+          <t>41385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68541</t>
+          <t>69578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>59568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>93634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487571</t>
+          <t>486963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506294</t>
+          <t>506644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447101</t>
+          <t>446064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473673</t>
+          <t>474257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>940798</t>
+          <t>941155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>976258</t>
+          <t>975221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32356</t>
+          <t>31531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49019</t>
+          <t>48186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77177</t>
+          <t>76670</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69316</t>
+          <t>67540</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>102121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>354354</t>
+          <t>355179</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372961</t>
+          <t>372387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326809</t>
+          <t>327316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>354967</t>
+          <t>355800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688144</t>
+          <t>688575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>721380</t>
+          <t>723156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62989</t>
+          <t>62045</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92277</t>
+          <t>91442</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80536</t>
+          <t>79447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113798</t>
+          <t>113477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263836</t>
+          <t>263303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280622</t>
+          <t>280505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250657</t>
+          <t>251492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279945</t>
+          <t>280889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521719</t>
+          <t>522040</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>554981</t>
+          <t>556070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>67517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100881</t>
+          <t>102902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84881</t>
+          <t>85605</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122889</t>
+          <t>122236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182378</t>
+          <t>181779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>198561</t>
+          <t>198786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>233027</t>
+          <t>231006</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>266514</t>
+          <t>266391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>420902</t>
+          <t>421555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>458910</t>
+          <t>458186</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>79996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119234</t>
+          <t>120579</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331117</t>
+          <t>326983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>402712</t>
+          <t>400540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>424119</t>
+          <t>419464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>505612</t>
+          <t>503578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3157309</t>
+          <t>3155964</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3196315</t>
+          <t>3196547</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2976485</t>
+          <t>2978657</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3048080</t>
+          <t>3052214</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6150129</t>
+          <t>6152163</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6231622</t>
+          <t>6236277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678941</t>
+          <t>679558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686142</t>
+          <t>686149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595892</t>
+          <t>596352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607326</t>
+          <t>607375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280223</t>
+          <t>1279383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1292412</t>
+          <t>1292383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>28238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54133</t>
+          <t>54797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>32315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62841</t>
+          <t>62269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665910</t>
+          <t>666533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679973</t>
+          <t>679993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655441</t>
+          <t>654777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681046</t>
+          <t>681336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1328596</t>
+          <t>1329168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1358489</t>
+          <t>1359122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54890</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36845</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66715</t>
+          <t>66097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>594880</t>
+          <t>595333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610153</t>
+          <t>610112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>559374</t>
+          <t>558700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>585810</t>
+          <t>584943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162165</t>
+          <t>1162783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192035</t>
+          <t>1192655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>45752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75813</t>
+          <t>74429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48226</t>
+          <t>50931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81776</t>
+          <t>81999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417652</t>
+          <t>417837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427382</t>
+          <t>427381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>371987</t>
+          <t>373371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>401361</t>
+          <t>402048</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>795453</t>
+          <t>795230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>829003</t>
+          <t>826298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70052</t>
+          <t>70437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81998</t>
+          <t>81817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292970</t>
+          <t>293826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305768</t>
+          <t>305663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>283944</t>
+          <t>283559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310788</t>
+          <t>311304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>581784</t>
+          <t>581965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>612821</t>
+          <t>611715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80521</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116079</t>
+          <t>115219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86168</t>
+          <t>86163</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>126800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234490</t>
+          <t>233937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246338</t>
+          <t>246471</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272900</t>
+          <t>273760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>308458</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>511583</t>
+          <t>512030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>552662</t>
+          <t>552667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56092</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>268434</t>
+          <t>268396</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>337083</t>
+          <t>331839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>301477</t>
+          <t>306249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>376641</t>
+          <t>379222</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3370687</t>
+          <t>3369621</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3398568</t>
+          <t>3397756</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3218015</t>
+          <t>3223259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3286664</t>
+          <t>3286702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6605236</t>
+          <t>6602655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6680400</t>
+          <t>6675628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585218</t>
+          <t>585208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>554110</t>
+          <t>554008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562604</t>
+          <t>562455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143067</t>
+          <t>1143041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152196</t>
+          <t>1152191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661494</t>
+          <t>661530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640344</t>
+          <t>641236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654578</t>
+          <t>654728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307891</t>
+          <t>1308207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1322469</t>
+          <t>1322835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>26701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50630</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42742</t>
+          <t>39828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72319</t>
+          <t>72072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615887</t>
+          <t>616543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635371</t>
+          <t>634664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598447</t>
+          <t>596789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623032</t>
+          <t>622376</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1222806</t>
+          <t>1223053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1252383</t>
+          <t>1255297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>35441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>62867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74186</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458724</t>
+          <t>458598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472929</t>
+          <t>472791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>434214</t>
+          <t>433982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>461954</t>
+          <t>461408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>900581</t>
+          <t>899543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>930191</t>
+          <t>931297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41534</t>
+          <t>41055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70281</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49823</t>
+          <t>49308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81209</t>
+          <t>80999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315193</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328717</t>
+          <t>329176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307481</t>
+          <t>307186</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336228</t>
+          <t>336707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630883</t>
+          <t>631093</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662269</t>
+          <t>662784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>46566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80647</t>
+          <t>81592</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56924</t>
+          <t>58300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94370</t>
+          <t>95157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237666</t>
+          <t>238712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251075</t>
+          <t>251104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319522</t>
+          <t>318577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351993</t>
+          <t>353603</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562797</t>
+          <t>562010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>600243</t>
+          <t>598867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66907</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187489</t>
+          <t>189281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>251019</t>
+          <t>249845</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>238950</t>
+          <t>235967</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>305143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3327443</t>
+          <t>3324768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3354627</t>
+          <t>3355209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3293523</t>
+          <t>3294697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3357053</t>
+          <t>3355261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6631318</t>
+          <t>6633749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6699942</t>
+          <t>6702925</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>308877</t>
+          <t>357748</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297815</t>
+          <t>345503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>708864</t>
+          <t>765541</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>694668</t>
+          <t>751795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,67 +10043,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>11988</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>20728</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>8670</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>3958</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>16707</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421194</t>
+          <t>474437</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415473</t>
+          <t>468357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,67 +10156,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>505187</t>
+          <t>491547</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498289</t>
+          <t>483979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509265</t>
+          <t>496289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>965985</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>957245</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>971843</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>98,77%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>926381</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>918344</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>931093</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24277</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43469</t>
+          <t>49740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44243</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>68574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>525251</t>
+          <t>607675</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515988</t>
+          <t>597096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531064</t>
+          <t>613377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>508643</t>
+          <t>582250</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>498330</t>
+          <t>571748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>592047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033894</t>
+          <t>1189925</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1020835</t>
+          <t>1173751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1044921</t>
+          <t>1201974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23049</t>
+          <t>25759</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37588</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86483</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71489</t>
+          <t>77264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101838</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61832</t>
+          <t>97719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137805</t>
+          <t>134097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>864737</t>
+          <t>674858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850198</t>
+          <t>662282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879046</t>
+          <t>684254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>625292</t>
+          <t>644668</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609937</t>
+          <t>628955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640286</t>
+          <t>658528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1490029</t>
+          <t>1319526</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1461756</t>
+          <t>1302312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1537729</t>
+          <t>1338690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735792</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711775</t>
+          <t>735792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599561</t>
+          <t>1436409</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599561</t>
+          <t>1436409</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599561</t>
+          <t>1436409</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38928</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>55148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73160</t>
+          <t>82367</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61762</t>
+          <t>70562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84830</t>
+          <t>97318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>112087</t>
+          <t>124263</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96291</t>
+          <t>106802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129257</t>
+          <t>143189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>521309</t>
+          <t>566463</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509472</t>
+          <t>553211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>530899</t>
+          <t>576609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>471568</t>
+          <t>524398</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>459898</t>
+          <t>509447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>482966</t>
+          <t>536203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>992877</t>
+          <t>1090861</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975707</t>
+          <t>1071935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1008673</t>
+          <t>1108322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104964</t>
+          <t>1215124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62603</t>
+          <t>69080</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>58143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99415</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>93501</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40166</t>
+          <t>80270</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111550</t>
+          <t>106683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>345763</t>
+          <t>381791</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>336968</t>
+          <t>372334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>352333</t>
+          <t>388745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>545765</t>
+          <t>370086</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>508953</t>
+          <t>358935</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580345</t>
+          <t>381023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>891528</t>
+          <t>751877</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>864264</t>
+          <t>738695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>935648</t>
+          <t>765108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975814</t>
+          <t>845378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100334</t>
+          <t>110226</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88542</t>
+          <t>96517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113299</t>
+          <t>125227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>125108</t>
+          <t>137795</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109600</t>
+          <t>121965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141643</t>
+          <t>154718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>257985</t>
+          <t>282629</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249858</t>
+          <t>272752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265525</t>
+          <t>290506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>325497</t>
+          <t>354383</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312532</t>
+          <t>339382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>337289</t>
+          <t>368092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>583482</t>
+          <t>637012</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>566947</t>
+          <t>620089</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598990</t>
+          <t>652842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93768</t>
+          <t>115239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145705</t>
+          <t>157044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>366375</t>
+          <t>406336</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>301167</t>
+          <t>379438</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>407814</t>
+          <t>439184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>488249</t>
+          <t>541595</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>428811</t>
+          <t>501568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>538558</t>
+          <t>578599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3336227</t>
+          <t>3395647</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3312396</t>
+          <t>3373862</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3364333</t>
+          <t>3415667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3290829</t>
+          <t>3325079</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3249390</t>
+          <t>3292231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3356037</t>
+          <t>3351977</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6627057</t>
+          <t>6720727</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6576748</t>
+          <t>6683723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6686495</t>
+          <t>6760754</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
